--- a/intern_schedule_2026-2027/schedules/TYP_Intern_Schedule_Sep2026-Jun2027.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_Intern_Schedule_Sep2026-Jun2027.xlsx
@@ -1178,12 +1178,12 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>AHLUWALIA Sr, LI</t>
+          <t>WISE, LI</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>WISE</t>
+          <t>AHLUWALIA Sr</t>
         </is>
       </c>
     </row>
@@ -1198,17 +1198,17 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
+          <t>WISE</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>BUTT, LI</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
           <t>AHLUWALIA Sr</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>BUTT, LI</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>WISE</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>BUTT, AHLUWALIA Sr</t>
+          <t>BUTT, WISE</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>WISE</t>
+          <t>AHLUWALIA Sr</t>
         </is>
       </c>
     </row>
@@ -2173,12 +2173,12 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
           <t>AHLUWALIA Sr</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -2552,13 +2552,13 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>AHLUWALIA Sr</t>
         </is>
       </c>
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>MACNEILLE  (24H)</t>
+          <t>AHLUWALIA Sr  (24H)</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>AHLUWALIA Sr</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="D20" s="6" t="n"/>
@@ -2594,12 +2594,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>CHIASSON</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE, CHIASSON</t>
+          <t>MACNEILLE, BRONSON</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>JUYAL</t>
         </is>
       </c>
       <c r="D33" s="6" t="n"/>
@@ -5935,12 +5935,12 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>JUYAL</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>FARZEELA, LI</t>
+          <t>FARZEELA, JUYAL</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">

--- a/intern_schedule_2026-2027/schedules/TYP_Intern_Schedule_Sep2026-Jun2027.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_Intern_Schedule_Sep2026-Jun2027.xlsx
@@ -3113,7 +3113,7 @@
       <c r="D3" s="6" t="n"/>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, MULLINS</t>
+          <t>CHIASSON, MULLINS</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -3153,17 +3153,17 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>WISE, MULLINS</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
           <t>KENNEDY</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>WISE, MULLINS</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -3183,12 +3183,12 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>WISE, KENNEDY</t>
+          <t>WISE, CHIASSON</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -3208,12 +3208,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
           <t>KENNEDY</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>MULLINS</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>WISE, MULLINS</t>
+          <t>WISE, KENNEDY</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -3280,7 +3280,7 @@
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -3295,17 +3295,17 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>SAEED U, WISE</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
           <t>CHIASSON</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>SAEED U, WISE</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -3325,12 +3325,12 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>CHIASSON, WISE</t>
+          <t>KENNEDY, WISE</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -3350,12 +3350,12 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>CHIASSON, SAEED U</t>
+          <t>KENNEDY, SAEED U</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -3370,17 +3370,17 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>SAEED U</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
           <t>CHIASSON</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>SAEED U</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -3400,12 +3400,12 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>CHIASSON, WISE</t>
+          <t>KENNEDY, WISE</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -4033,12 +4033,12 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE, SHETTY</t>
+          <t>BRONSON, SHETTY</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE, BRONSON</t>
+          <t>BRONSON, MACNEILLE</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -4083,12 +4083,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
           <t>MACNEILLE</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>BRONSON</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE, SHETTY</t>
+          <t>BRONSON, SHETTY</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -4154,13 +4154,13 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -4180,12 +4180,12 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>VILLANUEVA, MACNEILLE</t>
+          <t>VILLANUEVA, BRONSON</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -4205,12 +4205,12 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>VIVEKANANDAN, MACNEILLE</t>
+          <t>VIVEKANANDAN, BRONSON</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -4225,17 +4225,17 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>VIVEKANANDAN, VILLANUEVA</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
           <t>MACNEILLE</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>VIVEKANANDAN, VILLANUEVA</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -4280,12 +4280,12 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>VIVEKANANDAN, MACNEILLE</t>
+          <t>VIVEKANANDAN, BRONSON</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -4300,13 +4300,13 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="D14" s="5" t="n"/>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>MACNEILLE  (24H)</t>
+          <t>BRONSON  (24H)</t>
         </is>
       </c>
     </row>
@@ -4342,12 +4342,12 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE, SALAM</t>
+          <t>BRONSON, SALAM</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>BRONSON, SALAM</t>
+          <t>MACNEILLE, SALAM</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>BRONSON, MACNEILLE</t>
+          <t>MACNEILLE, BRONSON</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
           <t>BRONSON</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>MACNEILLE</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>BRONSON, SALAM</t>
+          <t>MACNEILLE, SALAM</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -4488,13 +4488,13 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
       <c r="D22" s="6" t="n"/>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -4514,12 +4514,12 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>SALAM, BRONSON</t>
+          <t>SALAM, MACNEILLE</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -4539,12 +4539,12 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>FARZEELA, BRONSON</t>
+          <t>FARZEELA, MACNEILLE</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -4559,17 +4559,17 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>FARZEELA, SALAM</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
           <t>BRONSON</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>FARZEELA, SALAM</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -4614,12 +4614,12 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>FARZEELA, BRONSON</t>
+          <t>FARZEELA, MACNEILLE</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -4634,13 +4634,13 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
       <c r="D28" s="5" t="n"/>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>BRONSON  (24H)</t>
+          <t>MACNEILLE  (24H)</t>
         </is>
       </c>
     </row>
@@ -4751,12 +4751,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
           <t>MACNEILLE</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>BRONSON</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -8020,7 +8020,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="D13" s="6" t="n"/>

--- a/intern_schedule_2026-2027/schedules/TYP_Intern_Schedule_Sep2026-Jun2027.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_Intern_Schedule_Sep2026-Jun2027.xlsx
@@ -3228,17 +3228,17 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>MULLINS</t>
+          <t>CHIASSON</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>WISE, KENNEDY</t>
+          <t>WISE, MULLINS</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>

--- a/intern_schedule_2026-2027/schedules/TYP_Intern_Schedule_Sep2026-Jun2027.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_Intern_Schedule_Sep2026-Jun2027.xlsx
@@ -3113,7 +3113,7 @@
       <c r="D3" s="6" t="n"/>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>CHIASSON, MULLINS</t>
+          <t>KENNEDY, MULLINS</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -3153,17 +3153,17 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>WISE, MULLINS</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
           <t>CHIASSON</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>WISE, MULLINS</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -3183,12 +3183,12 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>WISE, CHIASSON</t>
+          <t>WISE, KENNEDY</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -3208,12 +3208,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
           <t>CHIASSON</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -3228,17 +3228,17 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>WISE, MULLINS</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
           <t>CHIASSON</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>WISE, MULLINS</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -3280,7 +3280,7 @@
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -3295,17 +3295,17 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>SAEED U, WISE</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
           <t>KENNEDY</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>SAEED U, WISE</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -3325,12 +3325,12 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, WISE</t>
+          <t>CHIASSON, WISE</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -3350,12 +3350,12 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, SAEED U</t>
+          <t>CHIASSON, SAEED U</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -3370,17 +3370,17 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>SAEED U</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
           <t>KENNEDY</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>SAEED U</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -3400,12 +3400,12 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, WISE</t>
+          <t>CHIASSON, WISE</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>

--- a/intern_schedule_2026-2027/schedules/TYP_Intern_Schedule_Sep2026-Jun2027.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_Intern_Schedule_Sep2026-Jun2027.xlsx
@@ -3113,7 +3113,7 @@
       <c r="D3" s="6" t="n"/>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, MULLINS</t>
+          <t>CHIASSON, MULLINS</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -3153,17 +3153,17 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>WISE, MULLINS</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
           <t>KENNEDY</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>WISE, MULLINS</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -3183,12 +3183,12 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>WISE, KENNEDY</t>
+          <t>WISE, CHIASSON</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -3208,12 +3208,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
           <t>KENNEDY</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -3228,17 +3228,17 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
+          <t>CHIASSON</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>WISE, MULLINS</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
           <t>KENNEDY</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>WISE, MULLINS</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -3280,7 +3280,7 @@
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -3295,17 +3295,17 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>SAEED U, WISE</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
           <t>CHIASSON</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>SAEED U, WISE</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -3325,12 +3325,12 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>CHIASSON, WISE</t>
+          <t>KENNEDY, WISE</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -3350,12 +3350,12 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>CHIASSON, SAEED U</t>
+          <t>KENNEDY, SAEED U</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>
@@ -3370,17 +3370,17 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>SAEED U</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
           <t>CHIASSON</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>SAEED U</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -3400,12 +3400,12 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>CHIASSON, WISE</t>
+          <t>KENNEDY, WISE</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>CHIASSON</t>
         </is>
       </c>
     </row>

--- a/intern_schedule_2026-2027/schedules/TYP_Intern_Schedule_Sep2026-Jun2027.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_Intern_Schedule_Sep2026-Jun2027.xlsx
@@ -1178,12 +1178,12 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>WISE, LI</t>
+          <t>AHLUWALIA Sr, LI</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>AHLUWALIA Sr</t>
+          <t>WISE</t>
         </is>
       </c>
     </row>
@@ -1198,17 +1198,17 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
+          <t>AHLUWALIA Sr</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>BUTT, LI</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
           <t>WISE</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>BUTT, LI</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>AHLUWALIA Sr</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>BUTT, WISE</t>
+          <t>BUTT, AHLUWALIA Sr</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>AHLUWALIA Sr</t>
+          <t>WISE</t>
         </is>
       </c>
     </row>
@@ -2173,12 +2173,12 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>AHLUWALIA Sr</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>AHLUWALIA Sr</t>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -2198,12 +2198,12 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>BUTT, BRONSON</t>
+          <t>BUTT, MACNEILLE</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -2218,13 +2218,13 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>BRONSON  (24H)</t>
+          <t>MACNEILLE  (24H)</t>
         </is>
       </c>
     </row>
@@ -2260,12 +2260,12 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>BRONSON, BUTT</t>
+          <t>MACNEILLE, BUTT</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE, BUTT</t>
+          <t>BRONSON, BUTT</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE, BRONSON</t>
+          <t>BRONSON, MACNEILLE</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
           <t>MACNEILLE</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>BRONSON</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE, BUTT</t>
+          <t>BRONSON, BUTT</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -2406,13 +2406,13 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="D13" s="6" t="n"/>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -2432,12 +2432,12 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>MULLINS, MACNEILLE</t>
+          <t>MULLINS, BRONSON</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -2457,12 +2457,12 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>AHLUWALIA Sr, MACNEILLE</t>
+          <t>AHLUWALIA Sr, BRONSON</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -2477,17 +2477,17 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>AHLUWALIA Sr, MULLINS</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
           <t>MACNEILLE</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>AHLUWALIA Sr, MULLINS</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -2532,12 +2532,12 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>AHLUWALIA Sr, MACNEILLE</t>
+          <t>AHLUWALIA Sr, BRONSON</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -2552,13 +2552,13 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>AHLUWALIA Sr</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>AHLUWALIA Sr  (24H)</t>
+          <t>BRONSON  (24H)</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>AHLUWALIA Sr</t>
         </is>
       </c>
       <c r="D20" s="6" t="n"/>
@@ -2594,12 +2594,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE, BRONSON</t>
+          <t>BRONSON, CHIASSON</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>BRONSON, CHIASSON</t>
+          <t>MACNEILLE, CHIASSON</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>BRONSON, MACNEILLE</t>
+          <t>MACNEILLE, BRONSON</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -2669,12 +2669,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
           <t>BRONSON</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>MACNEILLE</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>BRONSON, CHIASSON</t>
+          <t>MACNEILLE, CHIASSON</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -2740,13 +2740,13 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
       <c r="D27" s="6" t="n"/>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -2766,12 +2766,12 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>CHIASSON, BRONSON</t>
+          <t>CHIASSON, MACNEILLE</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>MULLINS, BRONSON</t>
+          <t>MULLINS, MACNEILLE</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -2811,17 +2811,17 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
+          <t>MACNEILLE</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>MULLINS, CHIASSON</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
           <t>BRONSON</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>MULLINS, CHIASSON</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>MACNEILLE</t>
         </is>
       </c>
     </row>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -2866,12 +2866,12 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>MULLINS, BRONSON</t>
+          <t>MULLINS, MACNEILLE</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>MACNEILLE</t>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -2886,13 +2886,13 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>MACNEILLE</t>
         </is>
       </c>
       <c r="D33" s="5" t="n"/>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>BRONSON  (24H)</t>
+          <t>MACNEILLE  (24H)</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>Stephen MacNeille</t>
+          <t>Isaac Bronson</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2930,7 +2930,7 @@
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
-          <t>Isaac Bronson</t>
+          <t>Stephen MacNeille</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">

--- a/intern_schedule_2026-2027/schedules/TYP_Intern_Schedule_Sep2026-Jun2027.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_Intern_Schedule_Sep2026-Jun2027.xlsx
@@ -6102,12 +6102,12 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>ZAIDI</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>LI, ZAIDI</t>
+          <t>LI, KOPP VANUZZI</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI, ZAIDI</t>
+          <t>ZAIDI, KOPP VANUZZI</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -6152,12 +6152,12 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>KOPP VANUZZI</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI, LI</t>
+          <t>ZAIDI, LI</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>ZAIDI</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI, ZAIDI</t>
+          <t>ZAIDI, KOPP VANUZZI</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -6227,13 +6227,13 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>KOPP VANUZZI</t>
         </is>
       </c>
       <c r="D15" s="5" t="n"/>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>ZAIDI  (24H)</t>
+          <t>KOPP VANUZZI  (24H)</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>ZAIDI</t>
         </is>
       </c>
       <c r="D16" s="6" t="n"/>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI, KOPP VANUZZI</t>
+          <t>KOPP VANUZZI, ZAIDI</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>KOPP VANUZZI</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>VILLANUEVA, KOPP VANUZZI</t>
+          <t>VILLANUEVA, ZAIDI</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>ZAIDI</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>VILLANUEVA, ZAIDI</t>
+          <t>VILLANUEVA, KOPP VANUZZI</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>KOPP VANUZZI</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>KOPP VANUZZI</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>VILLANUEVA, KOPP VANUZZI</t>
+          <t>VILLANUEVA, ZAIDI</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -6394,13 +6394,13 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>ZAIDI</t>
         </is>
       </c>
       <c r="D22" s="5" t="n"/>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI  (24H)</t>
+          <t>ZAIDI  (24H)</t>
         </is>
       </c>
     </row>
@@ -6421,7 +6421,7 @@
       <c r="D23" s="6" t="n"/>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>KOPP VANUZZI</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI, VILLANUEVA</t>
+          <t>ZAIDI, VILLANUEVA</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>KOPP VANUZZI</t>
         </is>
       </c>
     </row>
@@ -6461,17 +6461,17 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>LI, VILLANUEVA</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
           <t>KOPP VANUZZI</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>LI, VILLANUEVA</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -6491,12 +6491,12 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>LI, KOPP VANUZZI</t>
+          <t>LI, ZAIDI</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>KOPP VANUZZI</t>
         </is>
       </c>
     </row>
@@ -6516,12 +6516,12 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
           <t>KOPP VANUZZI</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -6536,17 +6536,17 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>LI, VILLANUEVA</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
           <t>KOPP VANUZZI</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>LI, VILLANUEVA</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -6588,7 +6588,7 @@
       <c r="D30" s="6" t="n"/>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -6803,17 +6803,17 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
+          <t>KOPP VANUZZI</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>SHETTY, MATSUOKA</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
           <t>KENNEDY</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>SHETTY, MATSUOKA</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>KOPP VANUZZI</t>
         </is>
       </c>
     </row>
@@ -6833,12 +6833,12 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, MATSUOKA</t>
+          <t>KOPP VANUZZI, MATSUOKA</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -6858,12 +6858,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, SHETTY</t>
+          <t>KOPP VANUZZI, SHETTY</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -6878,17 +6878,17 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
+          <t>KOPP VANUZZI</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>SHETTY</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
           <t>KENNEDY</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>SHETTY</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>KOPP VANUZZI</t>
         </is>
       </c>
     </row>
@@ -6908,12 +6908,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, MATSUOKA</t>
+          <t>KOPP VANUZZI, MATSUOKA</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>KOPP VANUZZI</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -6949,7 +6949,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>KOPP VANUZZI</t>
         </is>
       </c>
       <c r="D9" s="6" t="n"/>
@@ -6970,12 +6970,12 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>KENNEDY</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA, KENNEDY</t>
+          <t>MATSUOKA, PATEL</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -7000,7 +7000,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>PATEL, KENNEDY</t>
+          <t>KENNEDY, PATEL</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -7020,12 +7020,12 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>PATEL</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>PATEL, MATSUOKA</t>
+          <t>KENNEDY, MATSUOKA</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>KENNEDY</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>PATEL, KENNEDY</t>
+          <t>KENNEDY, PATEL</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -7095,13 +7095,13 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>PATEL</t>
         </is>
       </c>
       <c r="D15" s="5" t="n"/>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>KENNEDY  (24H)</t>
+          <t>PATEL  (24H)</t>
         </is>
       </c>
     </row>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>KENNEDY</t>
         </is>
       </c>
       <c r="D16" s="6" t="n"/>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, PATEL</t>
+          <t>PATEL, KENNEDY</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>PATEL</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>BUTT, PATEL</t>
+          <t>BUTT, KENNEDY</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>KENNEDY</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>BUTT, KENNEDY</t>
+          <t>BUTT, PATEL</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>PATEL</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -7237,12 +7237,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>PATEL</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>BUTT, PATEL</t>
+          <t>BUTT, KENNEDY</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -7262,13 +7262,13 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>KENNEDY</t>
         </is>
       </c>
       <c r="D22" s="5" t="n"/>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>PATEL  (24H)</t>
+          <t>KENNEDY  (24H)</t>
         </is>
       </c>
     </row>
@@ -7289,7 +7289,7 @@
       <c r="D23" s="6" t="n"/>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>PATEL</t>
         </is>
       </c>
     </row>
@@ -7309,12 +7309,12 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>ALMADHOOB, BUTT</t>
+          <t>KENNEDY, BUTT</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>ALMADHOOB</t>
         </is>
       </c>
     </row>
@@ -7329,17 +7329,17 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA, BUTT</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
           <t>ALMADHOOB</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>MATSUOKA, BUTT</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -7359,12 +7359,12 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>MATSUOKA, ALMADHOOB</t>
+          <t>MATSUOKA, KENNEDY</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY</t>
+          <t>ALMADHOOB</t>
         </is>
       </c>
     </row>
@@ -7384,12 +7384,12 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
           <t>ALMADHOOB</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -7404,17 +7404,17 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
+          <t>KENNEDY</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>MATSUOKA, BUTT</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
           <t>ALMADHOOB</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>MATSUOKA, BUTT</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -7456,7 +7456,7 @@
       <c r="D30" s="6" t="n"/>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>ALMADHOOB</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -7471,17 +7471,17 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
+          <t>ALMADHOOB</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>RIVERA, MATSUOKA</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
           <t>KENNEDY</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>RIVERA, MATSUOKA</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>ALMADHOOB</t>
         </is>
       </c>
     </row>
@@ -7501,12 +7501,12 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, MATSUOKA</t>
+          <t>ALMADHOOB, MATSUOKA</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>ALMADHOOB</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -7526,12 +7526,12 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>KENNEDY, RIVERA</t>
+          <t>ALMADHOOB, RIVERA</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>ALMADHOOB</t>
+          <t>KENNEDY</t>
         </is>
       </c>
     </row>
@@ -7782,17 +7782,17 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
+          <t>ALMADHOOB</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>RIVERA</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
           <t>OGHENESUME</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>RIVERA</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>ALMADHOOB</t>
         </is>
       </c>
     </row>
@@ -7812,12 +7812,12 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>OGHENESUME, ZAIDI</t>
+          <t>ALMADHOOB, ZAIDI</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>ALMADHOOB</t>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>

--- a/intern_schedule_2026-2027/schedules/TYP_Intern_Schedule_Sep2026-Jun2027.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_Intern_Schedule_Sep2026-Jun2027.xlsx
@@ -3441,7 +3441,7 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>CHIASSON</t>
+          <t>KENNEDY</t>
         </is>
       </c>
       <c r="D17" s="6" t="n"/>
